--- a/experiment_output/TwoCombinedGames/ElapsedTimePerFilesOnebyOneBothCombinedGamesFinal.xlsx
+++ b/experiment_output/TwoCombinedGames/ElapsedTimePerFilesOnebyOneBothCombinedGamesFinal.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://westernsydneyedu-my.sharepoint.com/personal/90948045_westernsydney_edu_au/Documents/Eclipse Workspace/bandit_rule_game_theory_experiment_two_combined_games/experiment_output/TwoCombinedGames/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://westernsydneyedu-my.sharepoint.com/personal/90948045_westernsydney_edu_au/Documents/Documents/Thesis/TwoCombinedGames/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="8_{A8DF2246-83AA-4524-BB96-4A361D94C7E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D87CBE9F-A6EB-43D5-B26D-D2EDB99CF63A}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="8_{A8DF2246-83AA-4524-BB96-4A361D94C7E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B521733-E1BB-4FF1-9FA9-6E1496DB43C6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="11964" xr2:uid="{27182AD4-836B-4194-8287-A2C4FC030FAD}"/>
   </bookViews>
@@ -5701,6 +5701,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -6021,7 +6025,10 @@
   <dimension ref="A1:H22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="5" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9" customWidth="1"/>
+    <col min="2" max="2" width="9.44140625" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" customWidth="1"/>
+    <col min="4" max="5" width="9.5546875" customWidth="1"/>
     <col min="6" max="6" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6651,7 +6658,11 @@
   <dimension ref="A1:H22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="5" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.5546875" customWidth="1"/>
+    <col min="2" max="2" width="8.88671875" customWidth="1"/>
+    <col min="3" max="3" width="9.44140625" customWidth="1"/>
+    <col min="4" max="4" width="8.77734375" customWidth="1"/>
+    <col min="5" max="5" width="9.21875" customWidth="1"/>
     <col min="6" max="6" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
